--- a/diseases/d125/2005-2009.xlsx
+++ b/diseases/d125/2005-2009.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8871,7 +8871,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15552,7 +15552,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -15945,7 +15945,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -17910,7 +17910,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18696,7 +18696,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19089,7 +19089,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -19875,7 +19875,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20661,7 +20661,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21054,7 +21054,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -21840,7 +21840,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22233,7 +22233,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22626,7 +22626,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23019,7 +23019,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -23805,7 +23805,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24198,7 +24198,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">

--- a/diseases/d125/2005-2009.xlsx
+++ b/diseases/d125/2005-2009.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8871,7 +8871,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15552,7 +15552,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -15945,7 +15945,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -17910,7 +17910,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18696,7 +18696,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19089,7 +19089,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -19875,7 +19875,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20661,7 +20661,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21054,7 +21054,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -21840,7 +21840,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22233,7 +22233,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22626,7 +22626,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23019,7 +23019,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -23805,7 +23805,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24198,7 +24198,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
